--- a/RESULTS/tables/survival_c_index.xlsx
+++ b/RESULTS/tables/survival_c_index.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8537636252885398</v>
+        <v>0.8658327447202779</v>
       </c>
       <c r="C2" t="n">
         <v>23901</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8489797452725822</v>
+        <v>0.8602964579975539</v>
       </c>
       <c r="C3" t="n">
         <v>6216</v>
